--- a/ETL-Inicial/data/clima_transformado.xlsx
+++ b/ETL-Inicial/data/clima_transformado.xlsx
@@ -562,13 +562,13 @@
         <v>-74.083</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I2" t="n">
         <v>6</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
@@ -596,11 +596,11 @@
         <v>122</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46121.55208333334</v>
+        <v>46121.56111111111</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-04-09T18:14:29.788016</t>
+          <t>2026-04-09T18:27:53.278841</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-04-09 13:14:37</t>
+          <t>2026-04-09 13:28:07</t>
         </is>
       </c>
     </row>
@@ -645,13 +645,13 @@
         <v>-75.536</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="L3" t="n">
         <v>10</v>
@@ -679,11 +679,11 @@
         <v>116</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46121.55138888889</v>
+        <v>46121.56041666667</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-04-09T18:14:31.441905</t>
+          <t>2026-04-09T18:27:54.757128</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -697,11 +697,11 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-04-09 13:14:37</t>
+          <t>2026-04-09 13:28:07</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
         <v>176</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46121.55138888889</v>
+        <v>46121.56041666667</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-04-09T18:14:33.105913</t>
+          <t>2026-04-09T18:27:56.245914</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-04-09 13:14:37</t>
+          <t>2026-04-09 13:28:07</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="L5" t="n">
         <v>10</v>
@@ -845,11 +845,11 @@
         <v>116</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46121.55138888889</v>
+        <v>46121.56111111111</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:14:34.546171</t>
+          <t>2026-04-09T18:27:57.782867</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-04-09 13:14:37</t>
+          <t>2026-04-09 13:28:07</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" t="n">
         <v>75</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="L6" t="n">
         <v>10</v>
@@ -928,11 +928,11 @@
         <v>200</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46121.55208333334</v>
+        <v>46121.56041666667</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-04-09T18:14:36.005059</t>
+          <t>2026-04-09T18:27:59.278914</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -946,11 +946,11 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-04-09 13:14:37</t>
+          <t>2026-04-09 13:28:07</t>
         </is>
       </c>
     </row>
